--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,236 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122753117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57477</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öster om Örsjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>802448</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7174219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122753068</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57493</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öster om Örsjön, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>802446</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7174212</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B4" t="n">
-        <v>57477</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R4" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B5" t="n">
-        <v>57493</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R5" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R4" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R5" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R4" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R5" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R4" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R5" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R4" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R5" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60107-2024 artfynd.xlsx
+++ b/artfynd/A 60107-2024 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122753117</v>
+        <v>122753068</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802448</v>
+        <v>802446</v>
       </c>
       <c r="R4" t="n">
-        <v>7174219</v>
+        <v>7174212</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>gammalt bo i gammal gran med spillkråkehack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122753068</v>
+        <v>122753117</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802446</v>
+        <v>802448</v>
       </c>
       <c r="R5" t="n">
-        <v>7174212</v>
+        <v>7174219</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>gammalt bo i gammal gran med spillkråkehack</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
